--- a/Game/Collectible.xlsx
+++ b/Game/Collectible.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">leaf</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252 Patch 2</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">junk</t>
